--- a/18_Insurance_Actuarial/_template_INSURANCE.xlsx
+++ b/18_Insurance_Actuarial/_template_INSURANCE.xlsx
@@ -12,7 +12,9 @@
     <sheet name="Underwriting Ratios" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Loss Reserve Triangle" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Embedded Value" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Reserve Summary" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Profitability" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="RefreshLog" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
   <si>
     <t xml:space="preserve">[INSURER] — Insurance / Actuarial Model</t>
   </si>
@@ -74,7 +76,7 @@
     <t xml:space="preserve">&lt;100% = underwriting profit; &gt;100% = underwriting loss (offset by investment income)</t>
   </si>
   <si>
-    <t xml:space="preserve">Loss Development Triangle (cumulative paid losses, $)</t>
+    <t xml:space="preserve">Loss Development Triangle — chain-ladder (cumulative paid losses, $)</t>
   </si>
   <si>
     <t xml:space="preserve">Accident Yr \ Dev Yr</t>
@@ -98,6 +100,12 @@
     <t xml:space="preserve">Dev 6</t>
   </si>
   <si>
+    <t xml:space="preserve">Ultimate Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBNR</t>
+  </si>
+  <si>
     <t xml:space="preserve">AY2020</t>
   </si>
   <si>
@@ -116,10 +124,16 @@
     <t xml:space="preserve">AY2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Age-to-age development factors (link ratios) go below once 2+ diagonals of data exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultimate loss = latest diagonal x cumulative development factor (chain-ladder method)</t>
+    <t xml:space="preserve">Age-to-age factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDF to ultimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total ultimate / IBNR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard volume-weighted chain-ladder. Link factors use only accident years with data in both adjacent columns (upper-left triangle) — that's why each factor's denominator shrinks moving right.</t>
   </si>
   <si>
     <t xml:space="preserve">Embedded Value (life/health simplified)</t>
@@ -141,6 +155,60 @@
   </si>
   <si>
     <t xml:space="preserve">Value of new business (VNB) this period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve Adequacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case reserves (carried, $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total policyholder surplus / equity ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBNR (from Loss Reserve Triangle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total reserves (case + IBNR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBNR as % of total reserves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A rising share signals either faster growth or slower-than-assumed reporting/settlement — worth a reserve review either way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserves-to-surplus ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAIC rule of thumb: &gt;3.0x is a leverage warning sign for a P&amp;C carrier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Profitability (underwriting + investment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net investment income ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average policyholder surplus / equity ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underwriting result (earned premium x (1 - combined ratio))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total profit (underwriting result + net investment income)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return on equity (ROE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why combined ratio alone can mislead: a carrier can run &gt;100% combined and still be profitable if investment income (float x yield) covers the gap</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -165,12 +233,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,6 +307,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -313,7 +390,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -351,19 +428,31 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -623,7 +712,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -677,7 +766,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -768,12 +857,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:H13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:J18"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -803,108 +893,223 @@
       <c r="H4" s="9" t="s">
         <v>23</v>
       </c>
+      <c r="I4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <f aca="false">IFERROR(H5*H15,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <f aca="false">IFERROR(I5-H5,"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="str">
+        <f aca="false">IFERROR(G6*G15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J6" s="11" t="str">
+        <f aca="false">IFERROR(I6-G6,"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="str">
+        <f aca="false">IFERROR(F7*F15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J7" s="11" t="str">
+        <f aca="false">IFERROR(I7-F7,"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="str">
+        <f aca="false">IFERROR(E8*E15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J8" s="11" t="str">
+        <f aca="false">IFERROR(I8-E8,"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="str">
+        <f aca="false">IFERROR(D9*D15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J9" s="11" t="str">
+        <f aca="false">IFERROR(I9-D9,"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
         <v>31</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="str">
+        <f aca="false">IFERROR(C10*C15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J10" s="11" t="str">
+        <f aca="false">IFERROR(I10-C10,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="12" t="str">
+        <f aca="false">IFERROR(SUM(D5:D9)/SUM(C5:C9),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E14" s="12" t="str">
+        <f aca="false">IFERROR(SUM(E5:E8)/SUM(D5:D8),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F14" s="12" t="str">
+        <f aca="false">IFERROR(SUM(F5:F7)/SUM(E5:E7),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G14" s="12" t="str">
+        <f aca="false">IFERROR(SUM(G5:G6)/SUM(F5:F6),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H14" s="12" t="str">
+        <f aca="false">IFERROR(SUM(H5:H5)/SUM(G5:G5),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="12" t="str">
+        <f aca="false">IFERROR(D14*D15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D15" s="12" t="str">
+        <f aca="false">IFERROR(E14*E15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E15" s="12" t="str">
+        <f aca="false">IFERROR(F14*F15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F15" s="12" t="str">
+        <f aca="false">IFERROR(G14*G15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G15" s="12" t="str">
+        <f aca="false">IFERROR(H14*H15,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <f aca="false">SUM(I5:I10)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <f aca="false">SUM(J5:J10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +1129,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
@@ -934,12 +1139,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -947,7 +1152,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -955,7 +1160,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
@@ -963,7 +1168,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -971,16 +1176,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="C10" s="13" t="n">
         <f aca="false">C5+C6-C7-C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>0</v>
@@ -1002,8 +1207,192 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:D13"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <f aca="false">'Loss Reserve Triangle'!J17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <f aca="false">IFERROR(C5+C10,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="6" t="str">
+        <f aca="false">IFERROR(C10/C11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="15" t="str">
+        <f aca="false">IFERROR(C11/C6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D12"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="14" t="str">
+        <f aca="false">IFERROR('Underwriting Ratios'!C5*(1-'Underwriting Ratios'!C12),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="13" t="str">
+        <f aca="false">IFERROR(C10+C5,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <f aca="false">IFERROR(C11/C6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1014,95 +1403,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>44</v>
+      <c r="B4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/18_Insurance_Actuarial/_template_INSURANCE.xlsx
+++ b/18_Insurance_Actuarial/_template_INSURANCE.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Paid Triangle" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Chain Ladder" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Bornhuetter-Ferguson" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Underwriting" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Embedded Value" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Stress" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Checks" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Sources" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="RefreshLog" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paid Triangle" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain Ladder" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bornhuetter-Ferguson" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underwriting" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embedded Value" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
+    <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
+    <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
@@ -35,7 +42,7 @@
     <numFmt numFmtId="168" formatCode="0.0000x"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +90,20 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +120,18 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -120,11 +149,16 @@
         <color rgb="00111827"/>
       </top>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -157,6 +191,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -722,6 +765,664 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Simplified Embedded Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pre-tax operating income</t>
+        </is>
+      </c>
+      <c r="C5" s="14">
+        <f>Underwriting!C13</f>
+        <v/>
+      </c>
+      <c r="D5" s="14">
+        <f>Underwriting!D13</f>
+        <v/>
+      </c>
+      <c r="E5" s="14">
+        <f>Underwriting!E13</f>
+        <v/>
+      </c>
+      <c r="F5" s="14">
+        <f>Underwriting!F13</f>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f>Underwriting!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tax at 25%</t>
+        </is>
+      </c>
+      <c r="C6" s="14">
+        <f>MAX(0,C5*0.25)</f>
+        <v/>
+      </c>
+      <c r="D6" s="14">
+        <f>MAX(0,D5*0.25)</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>MAX(0,E5*0.25)</f>
+        <v/>
+      </c>
+      <c r="F6" s="14">
+        <f>MAX(0,F5*0.25)</f>
+        <v/>
+      </c>
+      <c r="G6" s="14">
+        <f>MAX(0,G5*0.25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>After-tax distributable earnings</t>
+        </is>
+      </c>
+      <c r="C7" s="14">
+        <f>C5-C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="14">
+        <f>D5-D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="14">
+        <f>E5-E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="14">
+        <f>F5-F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="14">
+        <f>G5-G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Risk margin charge</t>
+        </is>
+      </c>
+      <c r="C8" s="14">
+        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
+        <v/>
+      </c>
+      <c r="D8" s="14">
+        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
+        <v/>
+      </c>
+      <c r="E8" s="14">
+        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
+        <v/>
+      </c>
+      <c r="F8" s="14">
+        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Economic earnings</t>
+        </is>
+      </c>
+      <c r="C9" s="14">
+        <f>C7-C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
+        <f>D7-D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>E7-E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="14">
+        <f>F7-F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>G7-G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="C10" s="22">
+        <f>1/(1+Assumptions!$E$9)^1</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>1/(1+Assumptions!$E$9)^2</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>1/(1+Assumptions!$E$9)^3</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>1/(1+Assumptions!$E$9)^4</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>1/(1+Assumptions!$E$9)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PV economic earnings</t>
+        </is>
+      </c>
+      <c r="C11" s="14">
+        <f>C9*C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="14">
+        <f>D9*D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>E9*E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>F9*F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>G9*G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Adjusted net asset value</t>
+        </is>
+      </c>
+      <c r="C13" s="14">
+        <f>Assumptions!E14-'Bornhuetter-Ferguson'!H15*(1+Assumptions!E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Present value of future economic earnings</t>
+        </is>
+      </c>
+      <c r="C14" s="14">
+        <f>SUM(C11:G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Embedded value</t>
+        </is>
+      </c>
+      <c r="C15" s="14">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Economic and Regulatory Capital Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Capital component</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Premium risk</t>
+        </is>
+      </c>
+      <c r="C5" s="14">
+        <f>Underwriting!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="10">
+        <f>Assumptions!E15</f>
+        <v/>
+      </c>
+      <c r="E5" s="14">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Reserve risk</t>
+        </is>
+      </c>
+      <c r="C6" s="14">
+        <f>'Bornhuetter-Ferguson'!H15</f>
+        <v/>
+      </c>
+      <c r="D6" s="10">
+        <f>Assumptions!E16</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Asset risk</t>
+        </is>
+      </c>
+      <c r="C7" s="14">
+        <f>Assumptions!E12</f>
+        <v/>
+      </c>
+      <c r="D7" s="10">
+        <f>Assumptions!E17</f>
+        <v/>
+      </c>
+      <c r="E7" s="14">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Diversified capital requirement</t>
+        </is>
+      </c>
+      <c r="E9" s="14">
+        <f>SQRT(SUMSQ(E5:E7)+2*0.25*(E5*E6+E5*E7+E6*E7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Available capital</t>
+        </is>
+      </c>
+      <c r="E10" s="14">
+        <f>Assumptions!E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Capital coverage</t>
+        </is>
+      </c>
+      <c r="E11" s="16">
+        <f>IFERROR(E10/E9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Minimum coverage</t>
+        </is>
+      </c>
+      <c r="E12" s="16">
+        <f>Assumptions!E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Capital status</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>IF(E11&gt;=E12,"PASS","BREACH")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>E13="PASS"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>E13="FAIL"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>E13="REVIEW"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>E13="BREACH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Reserve and Capital Stress Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Loss ratio / Asset shock</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="16">
+        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="D5" s="16">
+        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="F5" s="16">
+        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="G5" s="16">
+        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C6" s="16">
+        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="D6" s="16">
+        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="E6" s="16">
+        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="G6" s="16">
+        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="16">
+        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C8" s="16">
+        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="G8" s="16">
+        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="16">
+        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:G9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00FCE4D6"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00E2F0D9"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -870,7 +1571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1033,7 +1734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1304,6 +2005,1341 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:F64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Insurance &amp; Actuarial — Institutional Decision Surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Model ID</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Insurance &amp; Actuarial</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Declared maturity</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Canonical builder</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>tools/builders/build_insurance_release.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Decision arena</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>actuarial, underwriting, finance, capital committee and regulator</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Committee artifact</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>reserve, profitability and capital pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Operating cadence</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>monthly reserve monitoring; quarterly close; annual assumption review</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Key decision outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ultimate loss and reserve</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>loss ratio and combined ratio</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>new-business and embedded value</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>base, downside and break-even outputs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>liquidity / funding requirement and binding constraint</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Insider questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Which accident years are driving development?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>What operational change broke historical comparability?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>How collectible are reinsurance balances?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Which assumption is owner-approved versus modeler judgement?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>What fails first and who must act?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>Scenario families</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F29" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>reserve deterioration</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>frequency / severity inflation</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>catastrophe event</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>data freshness / source failure</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>combined severe-but-plausible downside</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>Primary diligence documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D37" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E37" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F37" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>policy and claims triangles</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>actuarial methods and assumptions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>reinsurance treaties</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>approved model card and assumption register</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>independent validation and challenge record</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>Challenge tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E45" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>triangle monotonicity where appropriate</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>development factors bounded and explained</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>reserve roll-forward reconciles</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>source-to-model lineage is reproducible</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>units, signs, dates and legal definitions reconcile</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Known failure modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E53" s="30" t="inlineStr">
+        <is>
+          <t>Evidence / location</t>
+        </is>
+      </c>
+      <c r="F53" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>blindly selecting latest link ratios</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>mixing accident, report and policy year</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ignoring claims inflation regime change</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>stale vintage presented as current</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>decision output disconnected from a binding constraint</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>Regulatory / methodological anchors</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D61" s="30" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="E61" s="30" t="inlineStr">
+        <is>
+          <t>Applicability</t>
+        </is>
+      </c>
+      <c r="F61" s="30" t="inlineStr">
+        <is>
+          <t>Review note</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Federal Reserve SR 26-2 Model Risk Management</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>governance, validation, change control, monitoring</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Map explicitly</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NAIC Risk-Based Capital</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>risk-sensitive statutory capital</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://content.naic.org/insurance-topics/risk-based-capital</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Map explicitly</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>IFRS 17 Insurance Contracts</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>insurance measurement and risk release</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.ifrs.org/issued-standards/list-of-standards/ifrs-17-insurance-contracts/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Map explicitly</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="B52:F52"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation sqref="F14:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F22:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F30:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F38:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F46:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F54:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Independent Challenge, Override and Closure Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Challenge</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>Owner response</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>Closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>triangle monotonicity where appropriate</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>development factors bounded and explained</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>reserve roll-forward reconciles</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>source-to-model lineage is reproducible</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>units, signs, dates and legal definitions reconcile</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Source, Transformation, Ownership and Refresh Map</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Source class</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>System / provider</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>Transform</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>Downstream</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>claims transactions</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>paid/incurred and claim-id reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>exposure and premium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>earned/written definition</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>model governance evidence</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>per release</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>version, reviewer, sign-off and change log</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>decision-use snapshot</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>per decision</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>immutable as-of date and source receipt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TO MAP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="J5:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1709,7 +3745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2019,7 +4055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2206,9 +4242,8 @@
         <f>PRODUCT(K$5:$K$5)</f>
         <v/>
       </c>
-      <c r="L6" s="19">
-        <f>PRODUCT(L$5:$K$5)</f>
-        <v/>
+      <c r="L6" s="19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2604,7 +4639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2993,7 +5028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3299,662 +5334,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Simplified Embedded Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pre-tax operating income</t>
-        </is>
-      </c>
-      <c r="C5" s="14">
-        <f>Underwriting!C13</f>
-        <v/>
-      </c>
-      <c r="D5" s="14">
-        <f>Underwriting!D13</f>
-        <v/>
-      </c>
-      <c r="E5" s="14">
-        <f>Underwriting!E13</f>
-        <v/>
-      </c>
-      <c r="F5" s="14">
-        <f>Underwriting!F13</f>
-        <v/>
-      </c>
-      <c r="G5" s="14">
-        <f>Underwriting!G13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tax at 25%</t>
-        </is>
-      </c>
-      <c r="C6" s="14">
-        <f>MAX(0,C5*0.25)</f>
-        <v/>
-      </c>
-      <c r="D6" s="14">
-        <f>MAX(0,D5*0.25)</f>
-        <v/>
-      </c>
-      <c r="E6" s="14">
-        <f>MAX(0,E5*0.25)</f>
-        <v/>
-      </c>
-      <c r="F6" s="14">
-        <f>MAX(0,F5*0.25)</f>
-        <v/>
-      </c>
-      <c r="G6" s="14">
-        <f>MAX(0,G5*0.25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>After-tax distributable earnings</t>
-        </is>
-      </c>
-      <c r="C7" s="14">
-        <f>C5-C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="14">
-        <f>D5-D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="14">
-        <f>E5-E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="14">
-        <f>F5-F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="14">
-        <f>G5-G6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Risk margin charge</t>
-        </is>
-      </c>
-      <c r="C8" s="14">
-        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
-        <v/>
-      </c>
-      <c r="D8" s="14">
-        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
-        <v/>
-      </c>
-      <c r="E8" s="14">
-        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
-        <v/>
-      </c>
-      <c r="F8" s="14">
-        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
-        <v/>
-      </c>
-      <c r="G8" s="14">
-        <f>'Bornhuetter-Ferguson'!$H$15*Assumptions!$E$10*Assumptions!$E$19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Economic earnings</t>
-        </is>
-      </c>
-      <c r="C9" s="14">
-        <f>C7-C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="14">
-        <f>D7-D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>E7-E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="14">
-        <f>F7-F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="14">
-        <f>G7-G8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="C10" s="22">
-        <f>1/(1+Assumptions!$E$9)^1</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f>1/(1+Assumptions!$E$9)^2</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f>1/(1+Assumptions!$E$9)^3</f>
-        <v/>
-      </c>
-      <c r="F10" s="22">
-        <f>1/(1+Assumptions!$E$9)^4</f>
-        <v/>
-      </c>
-      <c r="G10" s="22">
-        <f>1/(1+Assumptions!$E$9)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PV economic earnings</t>
-        </is>
-      </c>
-      <c r="C11" s="14">
-        <f>C9*C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="14">
-        <f>D9*D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="14">
-        <f>E9*E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="14">
-        <f>F9*F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="14">
-        <f>G9*G10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Adjusted net asset value</t>
-        </is>
-      </c>
-      <c r="C13" s="14">
-        <f>Assumptions!E14-'Bornhuetter-Ferguson'!H15*(1+Assumptions!E10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Present value of future economic earnings</t>
-        </is>
-      </c>
-      <c r="C14" s="14">
-        <f>SUM(C11:G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Embedded value</t>
-        </is>
-      </c>
-      <c r="C15" s="14">
-        <f>C13+C14</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Economic and Regulatory Capital Screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Capital component</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Premium risk</t>
-        </is>
-      </c>
-      <c r="C5" s="14">
-        <f>Underwriting!C5</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>Assumptions!E15</f>
-        <v/>
-      </c>
-      <c r="E5" s="14">
-        <f>C5*D5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Reserve risk</t>
-        </is>
-      </c>
-      <c r="C6" s="14">
-        <f>'Bornhuetter-Ferguson'!H15</f>
-        <v/>
-      </c>
-      <c r="D6" s="10">
-        <f>Assumptions!E16</f>
-        <v/>
-      </c>
-      <c r="E6" s="14">
-        <f>C6*D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Asset risk</t>
-        </is>
-      </c>
-      <c r="C7" s="14">
-        <f>Assumptions!E12</f>
-        <v/>
-      </c>
-      <c r="D7" s="10">
-        <f>Assumptions!E17</f>
-        <v/>
-      </c>
-      <c r="E7" s="14">
-        <f>C7*D7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Diversified capital requirement</t>
-        </is>
-      </c>
-      <c r="E9" s="14">
-        <f>SQRT(SUMSQ(E5:E7)+2*0.25*(E5*E6+E5*E7+E6*E7))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Available capital</t>
-        </is>
-      </c>
-      <c r="E10" s="14">
-        <f>Assumptions!E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Capital coverage</t>
-        </is>
-      </c>
-      <c r="E11" s="16">
-        <f>IFERROR(E10/E9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Minimum coverage</t>
-        </is>
-      </c>
-      <c r="E12" s="16">
-        <f>Assumptions!E18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Capital status</t>
-        </is>
-      </c>
-      <c r="E13">
-        <f>IF(E11&gt;=E12,"PASS","BREACH")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>E13="PASS"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>E13="FAIL"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>E13="REVIEW"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>E13="BREACH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Reserve and Capital Stress Matrix</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Loss ratio / Asset shock</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="D4" s="23" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E4" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G4" s="23" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="16">
-        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="D5" s="16">
-        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="E5" s="16">
-        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="F5" s="16">
-        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="G5" s="16">
-        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B5))/Capital!$E$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C6" s="16">
-        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="D6" s="16">
-        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="E6" s="16">
-        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B6))/Capital!$E$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C7" s="16">
-        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="D7" s="16">
-        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="E7" s="16">
-        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="F7" s="16">
-        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="G7" s="16">
-        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B7))/Capital!$E$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C8" s="16">
-        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="D8" s="16">
-        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="E8" s="16">
-        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="F8" s="16">
-        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="G8" s="16">
-        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B8))/Capital!$E$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="16">
-        <f>(Assumptions!$E$14*(1+C$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="D9" s="16">
-        <f>(Assumptions!$E$14*(1+D$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="E9" s="16">
-        <f>(Assumptions!$E$14*(1+E$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="F9" s="16">
-        <f>(Assumptions!$E$14*(1+F$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
-        <v/>
-      </c>
-      <c r="G9" s="16">
-        <f>(Assumptions!$E$14*(1+G$4)-'Bornhuetter-Ferguson'!$H$15*(1+$B9))/Capital!$E$9</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:G9">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00FCE4D6"/>
-        <color rgb="00FFF2CC"/>
-        <color rgb="00E2F0D9"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>